--- a/datosPreguntasReaccionMedias.xlsx
+++ b/datosPreguntasReaccionMedias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF3C277-A92E-4549-BAE6-A4D50615FE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4AD068-E567-4BFB-A981-FF06B129D38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/datosPreguntasReaccionMedias.xlsx
+++ b/datosPreguntasReaccionMedias.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4AD068-E567-4BFB-A981-FF06B129D38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
